--- a/DER_agentes_ia.xlsx
+++ b/DER_agentes_ia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor63053237\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E7AB21E-0719-483D-9656-D997EABE02EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C814D7C-913F-49AF-A47B-3237D4139669}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{2A48C432-72A5-4098-99AF-527F220C0F47}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="121">
   <si>
     <t>nome</t>
   </si>
@@ -105,9 +105,6 @@
     <t>caracteristca</t>
   </si>
   <si>
-    <t>INT</t>
-  </si>
-  <si>
     <t>caractisticas</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>tipo_imovel</t>
   </si>
   <si>
-    <t>enum</t>
-  </si>
-  <si>
     <t>area_util_m2</t>
   </si>
   <si>
@@ -219,9 +213,6 @@
     <t>creci</t>
   </si>
   <si>
-    <t>Transicao</t>
-  </si>
-  <si>
     <t>id_cliente</t>
   </si>
   <si>
@@ -267,9 +258,6 @@
     <t>tipo_pessoa</t>
   </si>
   <si>
-    <t>estado_civel</t>
-  </si>
-  <si>
     <t>comprovante_residencial</t>
   </si>
   <si>
@@ -307,6 +295,99 @@
   </si>
   <si>
     <t>composicao_familiar</t>
+  </si>
+  <si>
+    <t>regiao</t>
+  </si>
+  <si>
+    <t>qtd_corretores</t>
+  </si>
+  <si>
+    <t>horario_atendimento</t>
+  </si>
+  <si>
+    <t>enum(disponivel, vendido, em_espera, em_negociacao, alugado, inativo)</t>
+  </si>
+  <si>
+    <t>enum(casa, apartamento, loja, galpao, cobertura, kitnet, lote, chacara, sala_comercial)</t>
+  </si>
+  <si>
+    <t>enum(nasc, poen, outros)</t>
+  </si>
+  <si>
+    <t>Float</t>
+  </si>
+  <si>
+    <t>esquina</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Flaot</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Int - PK- incremental</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>enum(otimo, bom, regular, ruim, pessimo)</t>
+  </si>
+  <si>
+    <t>Datetime</t>
+  </si>
+  <si>
+    <t>qtd_imov_vend</t>
+  </si>
+  <si>
+    <t>regiao_atuacao</t>
+  </si>
+  <si>
+    <t>meta_valor</t>
+  </si>
+  <si>
+    <t>enum(fisica, juridica)</t>
+  </si>
+  <si>
+    <t>enum(comprador, vendedor, inquilino, conjuge)</t>
+  </si>
+  <si>
+    <t>estado_civil</t>
+  </si>
+  <si>
+    <t>renda_comprovada</t>
+  </si>
+  <si>
+    <t>conjuge</t>
+  </si>
+  <si>
+    <t>Transacao</t>
+  </si>
+  <si>
+    <t>FK -&gt; Pessoa.id</t>
+  </si>
+  <si>
+    <t>vinculo_empregaticio</t>
+  </si>
+  <si>
+    <t>enum(clt, pj, informal)</t>
+  </si>
+  <si>
+    <t>data_inicio_vinculo</t>
+  </si>
+  <si>
+    <t>enum(venda, locacao)</t>
+  </si>
+  <si>
+    <t>FK -&gt; Regiao.id</t>
   </si>
 </sst>
 </file>
@@ -348,9 +429,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,22 +747,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BE2317-BB33-4787-BC7F-28DF3E14C7FA}">
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" customWidth="1"/>
+    <col min="18" max="18" width="16.42578125" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" customWidth="1"/>
+    <col min="22" max="23" width="13.7109375" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" customWidth="1"/>
+    <col min="26" max="26" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -692,30 +778,31 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="Q1" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="V1" s="1"/>
-      <c r="X1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W1" s="1"/>
+      <c r="Y1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -727,70 +814,83 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1"/>
       <c r="M2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O2" s="1"/>
       <c r="Q2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S2" s="1"/>
       <c r="U2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="1"/>
+      <c r="Y2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
       </c>
+      <c r="F3" t="s">
+        <v>102</v>
+      </c>
       <c r="I3" t="s">
         <v>1</v>
       </c>
+      <c r="J3" t="s">
+        <v>102</v>
+      </c>
       <c r="M3" t="s">
         <v>1</v>
       </c>
+      <c r="N3" t="s">
+        <v>102</v>
+      </c>
       <c r="Q3" t="s">
         <v>1</v>
       </c>
+      <c r="R3" t="s">
+        <v>102</v>
+      </c>
       <c r="U3" t="s">
         <v>1</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -798,22 +898,31 @@
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>101</v>
       </c>
       <c r="M4" t="s">
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="R4" t="s">
+        <v>109</v>
       </c>
       <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -821,22 +930,28 @@
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>101</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5" t="s">
+        <v>110</v>
+      </c>
+      <c r="U5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" t="s">
         <v>69</v>
       </c>
-      <c r="U5" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -844,19 +959,25 @@
         <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" t="s">
+        <v>7</v>
       </c>
       <c r="Q6" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y6" t="s">
         <v>70</v>
       </c>
-      <c r="U6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -864,22 +985,28 @@
         <v>14</v>
       </c>
       <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
-        <v>35</v>
+      <c r="M7" t="s">
+        <v>8</v>
       </c>
       <c r="Q7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y7" t="s">
         <v>71</v>
       </c>
-      <c r="U7" t="s">
-        <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -887,19 +1014,28 @@
         <v>15</v>
       </c>
       <c r="I8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" t="s">
         <v>36</v>
       </c>
-      <c r="J8" t="s">
-        <v>37</v>
+      <c r="M8" t="s">
+        <v>106</v>
       </c>
       <c r="Q8" t="s">
-        <v>79</v>
-      </c>
-      <c r="X8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="U8" t="s">
+        <v>64</v>
+      </c>
+      <c r="V8" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -912,14 +1048,17 @@
       <c r="J9" t="s">
         <v>22</v>
       </c>
+      <c r="M9" t="s">
+        <v>107</v>
+      </c>
       <c r="Q9" t="s">
-        <v>80</v>
-      </c>
-      <c r="X9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -930,19 +1069,22 @@
         <v>17</v>
       </c>
       <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s">
         <v>38</v>
       </c>
-      <c r="J10" t="s">
-        <v>39</v>
+      <c r="M10" t="s">
+        <v>108</v>
       </c>
       <c r="Q10" t="s">
-        <v>7</v>
-      </c>
-      <c r="X10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -950,16 +1092,16 @@
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q11" t="s">
-        <v>8</v>
-      </c>
-      <c r="X11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -967,163 +1109,264 @@
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>93</v>
       </c>
       <c r="Q12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
       <c r="I13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
         <v>41</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" t="s">
         <v>42</v>
       </c>
-      <c r="Q13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="I14" t="s">
+      <c r="J15" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
         <v>43</v>
       </c>
-      <c r="Q14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="I15" t="s">
+      <c r="J16" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="I17" t="s">
         <v>44</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="J17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="I16" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q16" t="s">
+    <row r="20" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q21" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I17" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q17" t="s">
+    <row r="22" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I18" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q19" t="s">
+    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q20" t="s">
+    <row r="24" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I23" t="s">
+    <row r="25" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
         <v>53</v>
       </c>
-      <c r="Q23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I24" t="s">
+      <c r="J25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I25" t="s">
+      <c r="J26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I26" t="s">
+    <row r="27" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
         <v>56</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I27" t="s">
+      <c r="J28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
         <v>58</v>
       </c>
-      <c r="J27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I28" t="s">
+      <c r="J29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="29" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="5:17" x14ac:dyDescent="0.25">
       <c r="I31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="5:17" x14ac:dyDescent="0.25">
       <c r="I32" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="J32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I33" t="s">
-        <v>91</v>
+        <v>87</v>
+      </c>
+      <c r="J33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J34" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
